--- a/95 Файлы/Допуск. Университет/Допуск. Университет. Интерлифт-Юг.xlsx
+++ b/95 Файлы/Допуск. Университет/Допуск. Университет. Интерлифт-Юг.xlsx
@@ -137,7 +137,7 @@
     <t>Генеральный директор</t>
   </si>
   <si>
-    <t>с 1.04.2026 по 30.04.2026</t>
+    <t>с 1.05.2026 по 31.05.2026</t>
   </si>
 </sst>
 </file>
@@ -296,38 +296,38 @@
     <xf numFmtId="14" fontId="6" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="3">
@@ -629,14 +629,14 @@
   <sheetData>
     <row r="1" spans="2:7" ht="19.149999999999999" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="2" spans="2:7" ht="41.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B2" s="12" t="s">
+      <c r="B2" s="20" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="12"/>
-      <c r="D2" s="12"/>
-      <c r="E2" s="12"/>
-      <c r="F2" s="12"/>
-      <c r="G2" s="12"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
     </row>
     <row r="3" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B3" s="2" t="s">
@@ -644,11 +644,11 @@
       </c>
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
-      <c r="E3" s="14" t="s">
+      <c r="E3" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="F3" s="14"/>
-      <c r="G3" s="14"/>
+      <c r="F3" s="21"/>
+      <c r="G3" s="21"/>
     </row>
     <row r="4" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B4" s="2" t="s">
@@ -656,11 +656,11 @@
       </c>
       <c r="C4" s="2"/>
       <c r="D4" s="2"/>
-      <c r="E4" s="15">
+      <c r="E4" s="22">
         <v>3</v>
       </c>
-      <c r="F4" s="15"/>
-      <c r="G4" s="15"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
     </row>
     <row r="5" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B5" s="2" t="s">
@@ -668,11 +668,11 @@
       </c>
       <c r="C5" s="2"/>
       <c r="D5" s="2"/>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="22" t="s">
         <v>36</v>
       </c>
-      <c r="F5" s="15"/>
-      <c r="G5" s="15"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="22"/>
     </row>
     <row r="6" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B6" s="2" t="s">
@@ -680,11 +680,11 @@
       </c>
       <c r="C6" s="2"/>
       <c r="D6" s="2"/>
-      <c r="E6" s="15" t="s">
+      <c r="E6" s="22" t="s">
         <v>27</v>
       </c>
-      <c r="F6" s="15"/>
-      <c r="G6" s="15"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
     </row>
     <row r="7" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B7" s="2" t="s">
@@ -692,11 +692,11 @@
       </c>
       <c r="C7" s="2"/>
       <c r="D7" s="2"/>
-      <c r="E7" s="15" t="s">
+      <c r="E7" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="F7" s="15"/>
-      <c r="G7" s="15"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="22"/>
     </row>
     <row r="8" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B8" s="2" t="s">
@@ -704,11 +704,11 @@
       </c>
       <c r="C8" s="2"/>
       <c r="D8" s="2"/>
-      <c r="E8" s="15" t="s">
+      <c r="E8" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="15"/>
-      <c r="G8" s="15"/>
+      <c r="F8" s="22"/>
+      <c r="G8" s="22"/>
     </row>
     <row r="9" spans="2:7" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B9" s="13" t="s">
@@ -716,21 +716,21 @@
       </c>
       <c r="C9" s="13"/>
       <c r="D9" s="13"/>
-      <c r="E9" s="15" t="s">
+      <c r="E9" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="F9" s="15"/>
-      <c r="G9" s="15"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="22"/>
     </row>
     <row r="10" spans="2:7" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B10" s="3"/>
       <c r="C10" s="4"/>
       <c r="D10" s="4"/>
-      <c r="E10" s="16" t="s">
+      <c r="E10" s="12" t="s">
         <v>13</v>
       </c>
-      <c r="F10" s="16"/>
-      <c r="G10" s="16"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
     </row>
     <row r="11" spans="2:7" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B11" s="5" t="s">
@@ -831,45 +831,45 @@
       <c r="G16" s="6"/>
     </row>
     <row r="17" spans="2:7" ht="39" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B17" s="20" t="s">
+      <c r="B17" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="C17" s="20"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="20"/>
-      <c r="F17" s="18" t="s">
+      <c r="C17" s="17"/>
+      <c r="D17" s="17"/>
+      <c r="E17" s="17"/>
+      <c r="F17" s="15" t="s">
         <v>16</v>
       </c>
-      <c r="G17" s="18"/>
+      <c r="G17" s="15"/>
     </row>
     <row r="18" spans="2:7" ht="33.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B18" s="21" t="s">
+      <c r="B18" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="C18" s="21"/>
-      <c r="D18" s="21"/>
-      <c r="E18" s="21"/>
-      <c r="F18" s="19" t="s">
+      <c r="C18" s="18"/>
+      <c r="D18" s="18"/>
+      <c r="E18" s="18"/>
+      <c r="F18" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="G18" s="19"/>
+      <c r="G18" s="16"/>
     </row>
     <row r="19" spans="2:7" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B19" s="22">
+      <c r="B19" s="19">
         <f ca="1">TODAY()</f>
-        <v>46112</v>
-      </c>
-      <c r="C19" s="22"/>
+        <v>46140</v>
+      </c>
+      <c r="C19" s="19"/>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
       <c r="F19" s="3"/>
       <c r="G19" s="3"/>
     </row>
     <row r="20" spans="2:7" ht="18.75" x14ac:dyDescent="0.3">
-      <c r="B20" s="17" t="s">
+      <c r="B20" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="C20" s="17"/>
+      <c r="C20" s="14"/>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
       <c r="F20" s="3"/>
@@ -877,14 +877,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="E10:G10"/>
-    <mergeCell ref="B15:G15"/>
-    <mergeCell ref="B20:C20"/>
-    <mergeCell ref="F17:G17"/>
-    <mergeCell ref="F18:G18"/>
-    <mergeCell ref="B17:E17"/>
-    <mergeCell ref="B18:E18"/>
-    <mergeCell ref="B19:C19"/>
     <mergeCell ref="B2:G2"/>
     <mergeCell ref="B9:D9"/>
     <mergeCell ref="E3:G3"/>
@@ -894,6 +886,14 @@
     <mergeCell ref="E7:G7"/>
     <mergeCell ref="E8:G8"/>
     <mergeCell ref="E9:G9"/>
+    <mergeCell ref="E10:G10"/>
+    <mergeCell ref="B15:G15"/>
+    <mergeCell ref="B20:C20"/>
+    <mergeCell ref="F17:G17"/>
+    <mergeCell ref="F18:G18"/>
+    <mergeCell ref="B17:E17"/>
+    <mergeCell ref="B18:E18"/>
+    <mergeCell ref="B19:C19"/>
   </mergeCells>
   <pageMargins left="0.31496062992125984" right="0.31496062992125984" top="0.55118110236220474" bottom="0.35433070866141736" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="82" fitToHeight="0" orientation="portrait" r:id="rId1"/>
